--- a/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/fr-ca.xlsx
+++ b/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/fr-ca.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\OneDrive\Documents\_Learn\Packaging.tutorial\OS.11\23H2\Expand\Install\Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8CDD47-E22E-4785-9ED8-1F091828E080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4878D52-33E8-4741-A7BB-8D362A389F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="27634" windowHeight="16629" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="5" r:id="rId1"/>
@@ -4374,22 +4374,22 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L34"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="8" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="84.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="50.3828125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.61328125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="16.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="120.69140625" style="3" customWidth="1"/>
-    <col min="8" max="10" width="16.69140625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="16.69140625" style="8" customWidth="1"/>
-    <col min="12" max="12" width="2.69140625" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.15234375" style="1" hidden="1"/>
+    <col min="1" max="1" width="2.6640625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="84.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="50.3984375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="20.59765625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="120.6640625" style="3" customWidth="1"/>
+    <col min="8" max="10" width="16.6640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="16.6640625" style="8" customWidth="1"/>
+    <col min="12" max="12" width="2.6640625" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.1328125" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4402,7 +4402,7 @@
       <c r="J1" s="2"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:12" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" ht="80.2" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="1"/>
       <c r="C2" s="4" t="s">
         <v>262</v>
@@ -4416,7 +4416,7 @@
       <c r="J2" s="6"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1"/>
       <c r="C3" s="7"/>
       <c r="D3" s="5"/>
@@ -4426,7 +4426,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:12" ht="5.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:12" ht="5.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -4436,7 +4436,7 @@
       <c r="J4" s="11"/>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:12" ht="62.7" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" ht="62.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B5" s="12"/>
       <c r="C5" s="12" t="s">
         <v>9</v>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="L5" s="8"/>
     </row>
-    <row r="6" spans="1:12" ht="111" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" ht="110.25" x14ac:dyDescent="0.45">
       <c r="B6" s="14"/>
       <c r="C6" s="15" t="s">
         <v>264</v>
@@ -4496,7 +4496,7 @@
       <c r="K6" s="14"/>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="1:12" ht="111" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:12" ht="110.25" x14ac:dyDescent="0.45">
       <c r="B7" s="14"/>
       <c r="C7" s="42" t="s">
         <v>263</v>
@@ -4525,7 +4525,7 @@
       <c r="K7" s="43"/>
       <c r="L7" s="8"/>
     </row>
-    <row r="8" spans="1:12" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:12" ht="20.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C8" s="14"/>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
@@ -4535,7 +4535,7 @@
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
     </row>
-    <row r="9" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B9" s="17"/>
       <c r="C9" s="18" t="s">
         <v>2</v>
@@ -4544,7 +4544,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B10" s="20"/>
       <c r="C10" s="21" t="s">
         <v>0</v>
@@ -4559,7 +4559,7 @@
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
     </row>
-    <row r="11" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B11" s="22"/>
       <c r="C11" s="21" t="s">
         <v>1</v>
@@ -4574,7 +4574,7 @@
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
     </row>
-    <row r="12" spans="1:12" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:12" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="8"/>
@@ -4584,14 +4584,14 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:12" ht="30" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:12" ht="30" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
     </row>
-    <row r="14" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -4602,7 +4602,7 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -4613,7 +4613,7 @@
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -4624,7 +4624,7 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -4635,7 +4635,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -4646,7 +4646,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -4657,7 +4657,7 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -4668,7 +4668,7 @@
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -4679,7 +4679,7 @@
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -4690,7 +4690,7 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -4701,7 +4701,7 @@
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
@@ -4712,7 +4712,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -4723,7 +4723,7 @@
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
@@ -4734,7 +4734,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -4745,7 +4745,7 @@
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
@@ -4756,7 +4756,7 @@
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
@@ -4767,7 +4767,7 @@
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
@@ -4778,7 +4778,7 @@
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
@@ -4789,7 +4789,7 @@
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
@@ -4800,7 +4800,7 @@
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
@@ -4811,7 +4811,7 @@
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
@@ -4870,29 +4870,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R136"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C2" s="4" t="s">
         <v>256</v>
       </c>
@@ -4900,7 +4900,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -4908,7 +4908,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -4916,7 +4916,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -4924,13 +4924,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -4938,7 +4938,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -4953,7 +4953,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -4967,7 +4967,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -4981,7 +4981,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -4995,7 +4995,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -5009,7 +5009,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -5023,7 +5023,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -5037,7 +5037,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -5051,7 +5051,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -5065,7 +5065,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -5079,7 +5079,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -5093,7 +5093,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -5107,7 +5107,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -5121,7 +5121,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -5135,7 +5135,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -5149,7 +5149,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -5163,7 +5163,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -5177,7 +5177,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -5191,7 +5191,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -5205,7 +5205,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -5219,7 +5219,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -5233,7 +5233,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -5247,7 +5247,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -5261,7 +5261,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -5275,7 +5275,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -5289,7 +5289,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -5303,7 +5303,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -5317,7 +5317,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -5331,7 +5331,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -5345,7 +5345,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -5359,7 +5359,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -5373,7 +5373,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -5387,7 +5387,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -5401,7 +5401,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -5415,7 +5415,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -5429,7 +5429,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -5443,7 +5443,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -5457,7 +5457,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -5471,7 +5471,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -5485,7 +5485,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -5499,7 +5499,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -5513,7 +5513,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -5527,7 +5527,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -5541,7 +5541,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -5555,7 +5555,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -5569,7 +5569,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -5583,7 +5583,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -5597,7 +5597,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C55" s="3">
         <v>47</v>
       </c>
@@ -5611,12 +5611,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C57" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C58" s="34" t="s">
         <v>7</v>
       </c>
@@ -5630,7 +5630,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C59" s="36">
         <v>1</v>
       </c>
@@ -5644,7 +5644,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C60" s="39">
         <v>2</v>
       </c>
@@ -5658,7 +5658,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C61" s="36">
         <v>3</v>
       </c>
@@ -5672,7 +5672,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C62" s="39">
         <v>4</v>
       </c>
@@ -5686,7 +5686,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C63" s="36">
         <v>5</v>
       </c>
@@ -5700,7 +5700,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C64" s="39">
         <v>6</v>
       </c>
@@ -5714,7 +5714,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="65" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C65" s="36">
         <v>7</v>
       </c>
@@ -5728,7 +5728,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="66" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C66" s="39">
         <v>8</v>
       </c>
@@ -5742,7 +5742,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="67" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C67" s="36">
         <v>9</v>
       </c>
@@ -5756,7 +5756,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="68" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C68" s="39">
         <v>10</v>
       </c>
@@ -5770,7 +5770,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="69" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C69" s="36">
         <v>11</v>
       </c>
@@ -5784,7 +5784,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="70" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C70" s="39">
         <v>12</v>
       </c>
@@ -5798,7 +5798,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="71" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C71" s="36">
         <v>13</v>
       </c>
@@ -5812,7 +5812,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="72" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C72" s="39">
         <v>14</v>
       </c>
@@ -5826,7 +5826,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="73" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C73" s="36">
         <v>15</v>
       </c>
@@ -5840,7 +5840,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="74" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C74" s="39">
         <v>16</v>
       </c>
@@ -5854,7 +5854,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="75" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C75" s="36">
         <v>17</v>
       </c>
@@ -5868,7 +5868,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="76" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C76" s="39">
         <v>18</v>
       </c>
@@ -5882,7 +5882,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="77" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C77" s="36">
         <v>19</v>
       </c>
@@ -5896,7 +5896,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="78" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C78" s="39">
         <v>20</v>
       </c>
@@ -5910,7 +5910,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="79" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C79" s="36">
         <v>21</v>
       </c>
@@ -5924,7 +5924,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="80" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C80" s="39">
         <v>22</v>
       </c>
@@ -5938,7 +5938,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="81" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C81" s="36">
         <v>23</v>
       </c>
@@ -5952,7 +5952,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="82" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C82" s="39">
         <v>24</v>
       </c>
@@ -5966,7 +5966,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="83" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C83" s="36">
         <v>25</v>
       </c>
@@ -5980,7 +5980,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C84" s="39">
         <v>26</v>
       </c>
@@ -5994,7 +5994,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="85" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C85" s="36">
         <v>27</v>
       </c>
@@ -6008,7 +6008,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="86" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C86" s="39">
         <v>28</v>
       </c>
@@ -6022,7 +6022,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="87" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C87" s="36">
         <v>29</v>
       </c>
@@ -6036,7 +6036,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="88" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C88" s="39">
         <v>30</v>
       </c>
@@ -6050,7 +6050,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="89" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C89" s="36">
         <v>31</v>
       </c>
@@ -6064,7 +6064,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="90" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C90" s="39">
         <v>32</v>
       </c>
@@ -6078,7 +6078,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="91" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C91" s="36">
         <v>33</v>
       </c>
@@ -6092,7 +6092,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="92" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C92" s="39">
         <v>34</v>
       </c>
@@ -6106,7 +6106,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="93" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C93" s="36">
         <v>35</v>
       </c>
@@ -6120,7 +6120,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="94" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C94" s="39">
         <v>36</v>
       </c>
@@ -6134,7 +6134,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="95" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C95" s="36">
         <v>37</v>
       </c>
@@ -6148,7 +6148,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="96" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C96" s="39">
         <v>38</v>
       </c>
@@ -6162,7 +6162,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="97" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C97" s="36">
         <v>39</v>
       </c>
@@ -6176,7 +6176,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="98" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C98" s="39">
         <v>40</v>
       </c>
@@ -6190,7 +6190,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="99" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C99" s="36">
         <v>41</v>
       </c>
@@ -6204,7 +6204,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="100" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C100" s="39">
         <v>42</v>
       </c>
@@ -6218,7 +6218,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="101" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C101" s="36">
         <v>43</v>
       </c>
@@ -6232,7 +6232,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="102" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C102" s="39">
         <v>44</v>
       </c>
@@ -6246,7 +6246,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="103" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C103" s="36">
         <v>45</v>
       </c>
@@ -6260,7 +6260,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="104" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C104" s="39">
         <v>46</v>
       </c>
@@ -6274,7 +6274,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="105" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C105" s="36">
         <v>47</v>
       </c>
@@ -6288,7 +6288,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="106" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C106" s="39">
         <v>48</v>
       </c>
@@ -6302,7 +6302,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="107" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C107" s="36">
         <v>49</v>
       </c>
@@ -6316,7 +6316,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="108" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C108" s="39">
         <v>50</v>
       </c>
@@ -6330,7 +6330,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="109" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C109" s="36">
         <v>51</v>
       </c>
@@ -6344,7 +6344,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="110" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C110" s="39">
         <v>52</v>
       </c>
@@ -6358,7 +6358,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="111" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C111" s="36">
         <v>53</v>
       </c>
@@ -6372,7 +6372,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="112" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C112" s="39">
         <v>54</v>
       </c>
@@ -6386,7 +6386,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="113" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C113" s="36">
         <v>55</v>
       </c>
@@ -6400,7 +6400,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="114" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C114" s="39">
         <v>56</v>
       </c>
@@ -6414,7 +6414,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="115" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C115" s="36">
         <v>57</v>
       </c>
@@ -6428,7 +6428,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="116" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C116" s="39">
         <v>58</v>
       </c>
@@ -6442,7 +6442,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="117" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C117" s="36">
         <v>59</v>
       </c>
@@ -6456,7 +6456,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="118" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C118" s="39">
         <v>60</v>
       </c>
@@ -6470,7 +6470,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="119" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C119" s="36">
         <v>61</v>
       </c>
@@ -6484,7 +6484,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="120" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C120" s="39">
         <v>62</v>
       </c>
@@ -6498,7 +6498,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="121" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C121" s="36">
         <v>63</v>
       </c>
@@ -6512,7 +6512,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="122" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C122" s="39">
         <v>64</v>
       </c>
@@ -6526,7 +6526,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="123" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C123" s="36">
         <v>65</v>
       </c>
@@ -6540,7 +6540,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="124" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C124" s="39">
         <v>66</v>
       </c>
@@ -6554,7 +6554,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="125" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C125" s="36">
         <v>67</v>
       </c>
@@ -6568,7 +6568,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="126" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C126" s="39">
         <v>68</v>
       </c>
@@ -6582,7 +6582,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="127" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C127" s="36">
         <v>69</v>
       </c>
@@ -6596,7 +6596,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="128" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C128" s="39">
         <v>70</v>
       </c>
@@ -6610,7 +6610,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="129" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C129" s="36">
         <v>71</v>
       </c>
@@ -6624,7 +6624,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="130" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C130" s="39">
         <v>72</v>
       </c>
@@ -6638,7 +6638,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="131" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C131" s="36">
         <v>73</v>
       </c>
@@ -6652,7 +6652,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="132" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C132" s="39">
         <v>74</v>
       </c>
@@ -6666,7 +6666,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="133" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C133" s="36">
         <v>75</v>
       </c>
@@ -6680,7 +6680,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="134" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C134" s="39">
         <v>76</v>
       </c>
@@ -6694,7 +6694,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="135" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C135" s="36">
         <v>77</v>
       </c>
@@ -6708,7 +6708,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="136" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C136" s="39">
         <v>78</v>
       </c>
@@ -6745,29 +6745,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R137"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C2" s="4" t="s">
         <v>257</v>
       </c>
@@ -6775,7 +6775,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -6783,7 +6783,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -6791,7 +6791,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -6799,13 +6799,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -6813,7 +6813,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -6828,7 +6828,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -6842,7 +6842,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -6856,7 +6856,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -6870,7 +6870,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -6884,7 +6884,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -6898,7 +6898,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -6912,7 +6912,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -6926,7 +6926,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -6940,7 +6940,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -6954,7 +6954,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -6968,7 +6968,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -6982,7 +6982,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -6996,7 +6996,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -7010,7 +7010,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -7024,7 +7024,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -7038,7 +7038,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -7052,7 +7052,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -7066,7 +7066,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -7080,7 +7080,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -7094,7 +7094,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -7108,7 +7108,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -7122,7 +7122,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -7136,7 +7136,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -7150,7 +7150,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -7164,7 +7164,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -7178,7 +7178,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -7192,7 +7192,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -7206,7 +7206,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -7220,7 +7220,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -7234,7 +7234,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -7248,7 +7248,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -7262,7 +7262,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -7276,7 +7276,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -7290,7 +7290,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -7304,7 +7304,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -7318,7 +7318,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -7332,7 +7332,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -7346,7 +7346,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -7360,7 +7360,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -7374,7 +7374,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -7388,7 +7388,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -7402,7 +7402,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -7416,7 +7416,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -7430,7 +7430,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -7444,7 +7444,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -7458,7 +7458,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -7472,12 +7472,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -7491,7 +7491,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -7505,7 +7505,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -7519,7 +7519,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -7533,7 +7533,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -7547,7 +7547,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -7561,7 +7561,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -7575,7 +7575,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -7596,7 +7596,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -7617,7 +7617,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -7638,7 +7638,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -7659,7 +7659,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -7680,7 +7680,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -7701,7 +7701,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -7722,7 +7722,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -7743,7 +7743,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -7764,7 +7764,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -7785,7 +7785,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -7806,7 +7806,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -7827,7 +7827,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -7848,7 +7848,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -7869,7 +7869,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -7890,7 +7890,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -7911,7 +7911,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -7932,7 +7932,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -7953,7 +7953,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -7974,7 +7974,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -7995,7 +7995,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -8016,7 +8016,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -8037,7 +8037,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -8058,7 +8058,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -8079,7 +8079,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -8100,7 +8100,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -8121,7 +8121,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -8142,7 +8142,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -8163,7 +8163,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -8184,7 +8184,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -8205,7 +8205,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -8226,7 +8226,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -8247,7 +8247,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -8268,7 +8268,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -8289,7 +8289,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -8310,7 +8310,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -8331,7 +8331,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -8352,7 +8352,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -8373,7 +8373,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -8394,7 +8394,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -8415,7 +8415,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -8436,7 +8436,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -8457,7 +8457,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -8478,7 +8478,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -8499,7 +8499,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -8520,7 +8520,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -8541,7 +8541,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -8562,7 +8562,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -8583,7 +8583,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -8604,7 +8604,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -8625,7 +8625,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -8646,7 +8646,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -8667,7 +8667,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -8688,7 +8688,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -8709,7 +8709,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -8730,7 +8730,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -8751,7 +8751,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -8772,7 +8772,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -8793,7 +8793,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -8814,7 +8814,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -8835,7 +8835,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -8856,7 +8856,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -8877,7 +8877,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -8898,7 +8898,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -8919,7 +8919,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -8940,7 +8940,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -8961,7 +8961,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -8982,7 +8982,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -9003,7 +9003,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
@@ -9024,7 +9024,7 @@
       <c r="J132" s="30"/>
       <c r="K132" s="30"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C133" s="39">
         <v>76</v>
       </c>
@@ -9038,7 +9038,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C134" s="36">
         <v>77</v>
       </c>
@@ -9052,7 +9052,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C135" s="39">
         <v>78</v>
       </c>
@@ -9066,7 +9066,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C136" s="36">
         <v>79</v>
       </c>
@@ -9080,7 +9080,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C137" s="39">
         <v>80</v>
       </c>
@@ -9117,29 +9117,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R137"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C2" s="4" t="s">
         <v>258</v>
       </c>
@@ -9147,7 +9147,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -9155,7 +9155,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -9163,7 +9163,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -9171,13 +9171,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -9185,7 +9185,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -9200,7 +9200,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -9214,7 +9214,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -9228,7 +9228,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -9242,7 +9242,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -9256,7 +9256,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -9270,7 +9270,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -9284,7 +9284,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -9298,7 +9298,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -9312,7 +9312,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -9326,7 +9326,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -9340,7 +9340,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -9354,7 +9354,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -9368,7 +9368,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -9382,7 +9382,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -9396,7 +9396,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -9410,7 +9410,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -9424,7 +9424,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -9438,7 +9438,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -9452,7 +9452,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -9466,7 +9466,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -9480,7 +9480,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -9494,7 +9494,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -9508,7 +9508,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -9522,7 +9522,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -9536,7 +9536,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -9550,7 +9550,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -9564,7 +9564,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -9578,7 +9578,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -9592,7 +9592,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -9606,7 +9606,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -9620,7 +9620,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -9634,7 +9634,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -9648,7 +9648,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -9662,7 +9662,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -9676,7 +9676,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -9690,7 +9690,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -9704,7 +9704,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -9718,7 +9718,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -9732,7 +9732,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -9746,7 +9746,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -9760,7 +9760,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -9774,7 +9774,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -9788,7 +9788,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -9802,7 +9802,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -9816,7 +9816,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -9830,7 +9830,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -9844,12 +9844,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -9863,7 +9863,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -9877,7 +9877,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -9891,7 +9891,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -9905,7 +9905,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -9919,7 +9919,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -9933,7 +9933,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -9947,7 +9947,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -9968,7 +9968,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -9989,7 +9989,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -10010,7 +10010,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -10031,7 +10031,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -10052,7 +10052,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -10073,7 +10073,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -10094,7 +10094,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -10115,7 +10115,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -10136,7 +10136,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -10157,7 +10157,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -10178,7 +10178,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -10199,7 +10199,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -10220,7 +10220,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -10241,7 +10241,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -10262,7 +10262,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -10283,7 +10283,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -10304,7 +10304,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -10325,7 +10325,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -10346,7 +10346,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -10367,7 +10367,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -10388,7 +10388,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -10409,7 +10409,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -10430,7 +10430,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -10451,7 +10451,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -10472,7 +10472,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -10493,7 +10493,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -10514,7 +10514,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -10535,7 +10535,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -10556,7 +10556,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -10577,7 +10577,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -10598,7 +10598,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -10619,7 +10619,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -10640,7 +10640,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -10661,7 +10661,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -10682,7 +10682,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -10703,7 +10703,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -10724,7 +10724,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -10745,7 +10745,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -10766,7 +10766,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -10787,7 +10787,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -10808,7 +10808,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -10829,7 +10829,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -10850,7 +10850,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -10871,7 +10871,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -10892,7 +10892,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -10913,7 +10913,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -10934,7 +10934,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -10955,7 +10955,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -10976,7 +10976,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -10997,7 +10997,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -11018,7 +11018,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -11039,7 +11039,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -11060,7 +11060,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -11081,7 +11081,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -11102,7 +11102,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -11123,7 +11123,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -11144,7 +11144,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -11165,7 +11165,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -11186,7 +11186,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -11207,7 +11207,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -11228,7 +11228,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -11249,7 +11249,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -11270,7 +11270,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -11291,7 +11291,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -11312,7 +11312,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -11333,7 +11333,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -11354,7 +11354,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -11375,7 +11375,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
@@ -11396,7 +11396,7 @@
       <c r="J132" s="30"/>
       <c r="K132" s="30"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C133" s="39">
         <v>76</v>
       </c>
@@ -11410,7 +11410,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C134" s="36">
         <v>77</v>
       </c>
@@ -11424,7 +11424,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C135" s="39">
         <v>78</v>
       </c>
@@ -11438,7 +11438,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C136" s="36">
         <v>79</v>
       </c>
@@ -11452,7 +11452,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C137" s="39">
         <v>80</v>
       </c>
@@ -11489,29 +11489,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R137"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C2" s="4" t="s">
         <v>259</v>
       </c>
@@ -11519,7 +11519,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -11527,7 +11527,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -11535,7 +11535,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -11543,13 +11543,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -11557,7 +11557,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -11572,7 +11572,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -11586,7 +11586,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -11600,7 +11600,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -11614,7 +11614,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -11628,7 +11628,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -11642,7 +11642,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -11656,7 +11656,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -11670,7 +11670,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -11684,7 +11684,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -11698,7 +11698,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -11712,7 +11712,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -11726,7 +11726,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -11740,7 +11740,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -11754,7 +11754,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -11768,7 +11768,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -11782,7 +11782,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -11796,7 +11796,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -11810,7 +11810,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -11824,7 +11824,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -11838,7 +11838,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -11852,7 +11852,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -11866,7 +11866,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -11880,7 +11880,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -11894,7 +11894,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -11908,7 +11908,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -11922,7 +11922,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -11936,7 +11936,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -11950,7 +11950,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -11964,7 +11964,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -11978,7 +11978,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -11992,7 +11992,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -12006,7 +12006,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -12020,7 +12020,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -12034,7 +12034,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -12048,7 +12048,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -12062,7 +12062,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -12076,7 +12076,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -12090,7 +12090,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -12104,7 +12104,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -12118,7 +12118,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -12132,7 +12132,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -12146,7 +12146,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -12160,7 +12160,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -12174,7 +12174,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -12188,7 +12188,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -12202,7 +12202,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -12216,12 +12216,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -12235,7 +12235,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -12249,7 +12249,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -12263,7 +12263,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -12277,7 +12277,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -12291,7 +12291,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -12305,7 +12305,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -12319,7 +12319,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -12340,7 +12340,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -12361,7 +12361,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -12382,7 +12382,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -12403,7 +12403,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -12424,7 +12424,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -12445,7 +12445,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -12466,7 +12466,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -12487,7 +12487,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -12508,7 +12508,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -12529,7 +12529,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -12550,7 +12550,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -12571,7 +12571,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -12592,7 +12592,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -12613,7 +12613,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -12634,7 +12634,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -12655,7 +12655,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -12676,7 +12676,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -12697,7 +12697,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -12718,7 +12718,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -12739,7 +12739,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -12760,7 +12760,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -12781,7 +12781,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -12802,7 +12802,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -12823,7 +12823,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -12844,7 +12844,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -12865,7 +12865,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -12886,7 +12886,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -12907,7 +12907,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -12928,7 +12928,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -12949,7 +12949,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -12970,7 +12970,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -12991,7 +12991,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -13012,7 +13012,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -13033,7 +13033,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -13054,7 +13054,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -13075,7 +13075,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -13096,7 +13096,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -13117,7 +13117,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -13138,7 +13138,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -13159,7 +13159,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -13180,7 +13180,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -13201,7 +13201,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -13222,7 +13222,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -13243,7 +13243,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -13264,7 +13264,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -13285,7 +13285,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -13306,7 +13306,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -13327,7 +13327,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -13348,7 +13348,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -13369,7 +13369,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -13390,7 +13390,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -13411,7 +13411,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -13432,7 +13432,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -13453,7 +13453,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -13474,7 +13474,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -13495,7 +13495,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -13516,7 +13516,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -13537,7 +13537,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -13558,7 +13558,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -13579,7 +13579,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -13600,7 +13600,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -13621,7 +13621,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -13642,7 +13642,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -13663,7 +13663,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -13684,7 +13684,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -13705,7 +13705,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -13726,7 +13726,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -13747,7 +13747,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
@@ -13768,7 +13768,7 @@
       <c r="J132" s="30"/>
       <c r="K132" s="30"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C133" s="39">
         <v>76</v>
       </c>
@@ -13782,7 +13782,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C134" s="36">
         <v>77</v>
       </c>
@@ -13796,7 +13796,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C135" s="3">
         <v>78</v>
       </c>
@@ -13810,7 +13810,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C136" s="36">
         <v>79</v>
       </c>
@@ -13824,7 +13824,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C137" s="3">
         <v>80</v>
       </c>
@@ -13861,29 +13861,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R137"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C2" s="4" t="s">
         <v>260</v>
       </c>
@@ -13891,7 +13891,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -13899,7 +13899,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -13907,7 +13907,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -13915,13 +13915,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -13929,7 +13929,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -13944,7 +13944,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -13958,7 +13958,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -13972,7 +13972,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -13986,7 +13986,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -14000,7 +14000,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -14014,7 +14014,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -14028,7 +14028,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -14042,7 +14042,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -14056,7 +14056,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -14070,7 +14070,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -14084,7 +14084,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -14098,7 +14098,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -14112,7 +14112,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -14126,7 +14126,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -14140,7 +14140,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -14154,7 +14154,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -14168,7 +14168,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -14182,7 +14182,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -14196,7 +14196,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -14210,7 +14210,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -14224,7 +14224,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -14238,7 +14238,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -14252,7 +14252,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -14266,7 +14266,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -14280,7 +14280,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -14294,7 +14294,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -14308,7 +14308,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -14322,7 +14322,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -14336,7 +14336,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -14350,7 +14350,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -14364,7 +14364,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -14378,7 +14378,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -14392,7 +14392,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -14406,7 +14406,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -14420,7 +14420,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -14434,7 +14434,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -14448,7 +14448,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -14462,7 +14462,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -14476,7 +14476,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -14490,7 +14490,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -14504,7 +14504,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -14518,7 +14518,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -14532,7 +14532,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -14546,7 +14546,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -14560,7 +14560,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -14574,7 +14574,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -14588,12 +14588,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -14607,7 +14607,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -14621,7 +14621,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -14635,7 +14635,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -14649,7 +14649,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -14663,7 +14663,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -14677,7 +14677,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -14691,7 +14691,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -14712,7 +14712,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -14733,7 +14733,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -14754,7 +14754,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -14775,7 +14775,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -14796,7 +14796,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -14817,7 +14817,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -14838,7 +14838,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -14859,7 +14859,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -14880,7 +14880,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -14901,7 +14901,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -14922,7 +14922,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -14943,7 +14943,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -14964,7 +14964,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -14985,7 +14985,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -15006,7 +15006,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -15027,7 +15027,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -15048,7 +15048,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -15069,7 +15069,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -15090,7 +15090,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -15111,7 +15111,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -15132,7 +15132,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -15153,7 +15153,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -15174,7 +15174,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -15195,7 +15195,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -15216,7 +15216,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -15237,7 +15237,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -15258,7 +15258,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -15279,7 +15279,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -15300,7 +15300,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -15321,7 +15321,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -15342,7 +15342,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -15363,7 +15363,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -15384,7 +15384,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -15405,7 +15405,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -15426,7 +15426,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -15447,7 +15447,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -15468,7 +15468,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -15489,7 +15489,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -15510,7 +15510,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -15531,7 +15531,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -15552,7 +15552,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -15573,7 +15573,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -15594,7 +15594,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -15615,7 +15615,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -15636,7 +15636,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -15657,7 +15657,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -15678,7 +15678,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -15699,7 +15699,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -15720,7 +15720,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -15741,7 +15741,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -15762,7 +15762,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -15783,7 +15783,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -15804,7 +15804,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -15825,7 +15825,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -15846,7 +15846,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -15867,7 +15867,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -15888,7 +15888,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -15909,7 +15909,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -15930,7 +15930,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -15951,7 +15951,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -15972,7 +15972,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -15993,7 +15993,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -16014,7 +16014,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -16035,7 +16035,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -16056,7 +16056,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -16077,7 +16077,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -16098,7 +16098,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -16119,7 +16119,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
@@ -16140,7 +16140,7 @@
       <c r="J132" s="30"/>
       <c r="K132" s="30"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C133" s="39">
         <v>76</v>
       </c>
@@ -16154,7 +16154,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C134" s="36">
         <v>77</v>
       </c>
@@ -16168,7 +16168,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C135" s="3">
         <v>78</v>
       </c>
@@ -16182,7 +16182,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C136" s="36">
         <v>79</v>
       </c>
@@ -16196,7 +16196,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C137" s="3">
         <v>80</v>
       </c>
@@ -16233,29 +16233,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R137"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.150000000000006" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C2" s="4" t="s">
         <v>261</v>
       </c>
@@ -16263,7 +16263,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -16271,7 +16271,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -16279,7 +16279,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -16287,13 +16287,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -16301,7 +16301,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -16316,7 +16316,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -16330,7 +16330,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -16344,7 +16344,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -16358,7 +16358,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -16372,7 +16372,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -16386,7 +16386,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -16400,7 +16400,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -16414,7 +16414,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -16428,7 +16428,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -16442,7 +16442,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -16456,7 +16456,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -16470,7 +16470,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -16484,7 +16484,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -16498,7 +16498,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -16512,7 +16512,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -16526,7 +16526,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -16540,7 +16540,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -16554,7 +16554,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -16568,7 +16568,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -16582,7 +16582,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -16596,7 +16596,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -16610,7 +16610,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -16624,7 +16624,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -16638,7 +16638,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -16652,7 +16652,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -16666,7 +16666,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -16680,7 +16680,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -16694,7 +16694,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -16708,7 +16708,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -16722,7 +16722,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -16736,7 +16736,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -16750,7 +16750,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -16764,7 +16764,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -16778,7 +16778,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -16792,7 +16792,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -16806,7 +16806,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -16820,7 +16820,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -16834,7 +16834,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -16848,7 +16848,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -16862,7 +16862,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -16876,7 +16876,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -16890,7 +16890,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -16904,7 +16904,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -16918,7 +16918,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -16932,7 +16932,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -16946,7 +16946,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -16960,12 +16960,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -16979,7 +16979,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -16993,7 +16993,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -17007,7 +17007,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -17021,7 +17021,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -17035,7 +17035,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -17049,7 +17049,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -17063,7 +17063,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -17084,7 +17084,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -17105,7 +17105,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -17126,7 +17126,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -17147,7 +17147,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -17168,7 +17168,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -17189,7 +17189,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -17210,7 +17210,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -17231,7 +17231,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -17252,7 +17252,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -17273,7 +17273,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -17294,7 +17294,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -17315,7 +17315,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -17336,7 +17336,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -17357,7 +17357,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -17378,7 +17378,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -17399,7 +17399,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -17420,7 +17420,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -17441,7 +17441,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -17462,7 +17462,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -17483,7 +17483,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -17504,7 +17504,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -17525,7 +17525,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -17546,7 +17546,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -17567,7 +17567,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -17588,7 +17588,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -17609,7 +17609,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -17630,7 +17630,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -17651,7 +17651,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -17672,7 +17672,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -17693,7 +17693,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -17714,7 +17714,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -17735,7 +17735,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -17756,7 +17756,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -17777,7 +17777,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -17798,7 +17798,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -17819,7 +17819,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -17840,7 +17840,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -17861,7 +17861,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -17882,7 +17882,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -17903,7 +17903,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -17924,7 +17924,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -17945,7 +17945,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -17966,7 +17966,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -17987,7 +17987,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -18008,7 +18008,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -18029,7 +18029,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -18050,7 +18050,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -18071,7 +18071,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -18092,7 +18092,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -18113,7 +18113,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -18134,7 +18134,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -18155,7 +18155,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -18176,7 +18176,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -18197,7 +18197,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -18218,7 +18218,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -18239,7 +18239,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -18260,7 +18260,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -18281,7 +18281,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -18302,7 +18302,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -18323,7 +18323,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -18344,7 +18344,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -18365,7 +18365,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -18386,7 +18386,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -18407,7 +18407,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -18428,7 +18428,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -18449,7 +18449,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -18470,7 +18470,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -18491,7 +18491,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
@@ -18512,7 +18512,7 @@
       <c r="J132" s="30"/>
       <c r="K132" s="30"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C133" s="39">
         <v>76</v>
       </c>
@@ -18526,7 +18526,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C134" s="36">
         <v>77</v>
       </c>
@@ -18540,7 +18540,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C135" s="3">
         <v>78</v>
       </c>
@@ -18554,7 +18554,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C136" s="36">
         <v>79</v>
       </c>
@@ -18568,7 +18568,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C137" s="3">
         <v>80</v>
       </c>

--- a/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/fr-ca.xlsx
+++ b/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/fr-ca.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\OneDrive\Documents\_Learn\Packaging.tutorial\OS.11\23H2\Expand\Install\Report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5924f5d6bcb7c7fc/Documents/_Learn/Packaging.tutorial/OS.11/23H2/Expand/Install/Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4878D52-33E8-4741-A7BB-8D362A389F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{E4878D52-33E8-4741-A7BB-8D362A389F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A091DDEB-4D9C-4F2B-8722-D72EFEB5C600}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="27634" windowHeight="16629" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="5" r:id="rId1"/>
@@ -4374,22 +4374,22 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L34"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="0" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="8" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="84.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="50.3984375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.59765625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="120.6640625" style="3" customWidth="1"/>
-    <col min="8" max="10" width="16.6640625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="16.6640625" style="8" customWidth="1"/>
-    <col min="12" max="12" width="2.6640625" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.1328125" style="1" hidden="1"/>
+    <col min="1" max="1" width="2.69140625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="84.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="50.3828125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="20.61328125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="16.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="120.69140625" style="3" customWidth="1"/>
+    <col min="8" max="10" width="16.69140625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="16.69140625" style="8" customWidth="1"/>
+    <col min="12" max="12" width="2.69140625" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.15234375" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4402,7 +4402,7 @@
       <c r="J1" s="2"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:12" ht="80.2" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:12" ht="80.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1"/>
       <c r="C2" s="4" t="s">
         <v>262</v>
@@ -4416,7 +4416,7 @@
       <c r="J2" s="6"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1"/>
       <c r="C3" s="7"/>
       <c r="D3" s="5"/>
@@ -4426,7 +4426,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:12" ht="5.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -4436,7 +4436,7 @@
       <c r="J4" s="11"/>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:12" ht="62.75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" ht="62.8" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="12"/>
       <c r="C5" s="12" t="s">
         <v>9</v>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="L5" s="8"/>
     </row>
-    <row r="6" spans="1:12" ht="110.25" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" ht="111" x14ac:dyDescent="0.4">
       <c r="B6" s="14"/>
       <c r="C6" s="15" t="s">
         <v>264</v>
@@ -4496,7 +4496,7 @@
       <c r="K6" s="14"/>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="1:12" ht="110.25" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" ht="111" x14ac:dyDescent="0.4">
       <c r="B7" s="14"/>
       <c r="C7" s="42" t="s">
         <v>263</v>
@@ -4525,17 +4525,13 @@
       <c r="K7" s="43"/>
       <c r="L7" s="8"/>
     </row>
-    <row r="8" spans="1:12" ht="20.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" s="15" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="8"/>
+      <c r="B8" s="3"/>
       <c r="C8" s="14"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-    </row>
-    <row r="9" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="9" spans="1:12" s="3" customFormat="1" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="8"/>
       <c r="B9" s="17"/>
       <c r="C9" s="18" t="s">
         <v>2</v>
@@ -4544,7 +4540,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:12" s="8" customFormat="1" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B10" s="20"/>
       <c r="C10" s="21" t="s">
         <v>0</v>
@@ -4552,14 +4548,8 @@
       <c r="D10" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-    </row>
-    <row r="11" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+    </row>
+    <row r="11" spans="1:12" s="8" customFormat="1" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B11" s="22"/>
       <c r="C11" s="21" t="s">
         <v>1</v>
@@ -4567,14 +4557,8 @@
       <c r="D11" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-    </row>
-    <row r="12" spans="1:12" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="12" spans="1:12" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="8"/>
@@ -4584,14 +4568,14 @@
       <c r="I12" s="8"/>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:12" ht="30" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:12" ht="30" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
     </row>
-    <row r="14" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -4602,7 +4586,7 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
     </row>
-    <row r="15" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -4613,7 +4597,7 @@
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -4624,7 +4608,7 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
@@ -4635,7 +4619,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -4646,7 +4630,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -4657,7 +4641,7 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -4668,7 +4652,7 @@
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
@@ -4679,7 +4663,7 @@
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
@@ -4690,7 +4674,7 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -4701,7 +4685,7 @@
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
@@ -4712,7 +4696,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -4723,7 +4707,7 @@
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
@@ -4734,7 +4718,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -4745,7 +4729,7 @@
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
@@ -4756,7 +4740,7 @@
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
@@ -4767,7 +4751,7 @@
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
@@ -4778,7 +4762,7 @@
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
@@ -4789,7 +4773,7 @@
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
@@ -4800,7 +4784,7 @@
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
@@ -4811,7 +4795,7 @@
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" s="8" customFormat="1" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
@@ -4825,7 +4809,7 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <dataConsolidate/>
-  <conditionalFormatting sqref="F8:I1048576 F1:I1 H2:J5">
+  <conditionalFormatting sqref="F12:I1048576 F1:I1 H2:J5">
     <cfRule type="iconSet" priority="282">
       <iconSet iconSet="3Symbols2" showValue="0">
         <cfvo type="percent" val="0"/>
@@ -4844,7 +4828,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:I8 H6:J7" xr:uid="{23AE6323-BC7F-40E9-A5AD-9DE77137CC3B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H6:J7" xr:uid="{23AE6323-BC7F-40E9-A5AD-9DE77137CC3B}">
       <formula1>"1,0"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4870,29 +4854,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R136"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>256</v>
       </c>
@@ -4900,7 +4884,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -4908,7 +4892,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -4916,7 +4900,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -4924,13 +4908,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -4938,7 +4922,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -4953,7 +4937,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -4967,7 +4951,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -4981,7 +4965,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -4995,7 +4979,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -5009,7 +4993,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -5023,7 +5007,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -5037,7 +5021,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -5051,7 +5035,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -5065,7 +5049,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -5079,7 +5063,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -5093,7 +5077,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -5107,7 +5091,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -5121,7 +5105,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -5135,7 +5119,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -5149,7 +5133,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -5163,7 +5147,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -5177,7 +5161,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -5191,7 +5175,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -5205,7 +5189,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -5219,7 +5203,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -5233,7 +5217,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -5247,7 +5231,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -5261,7 +5245,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -5275,7 +5259,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -5289,7 +5273,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -5303,7 +5287,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -5317,7 +5301,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -5331,7 +5315,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -5345,7 +5329,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -5359,7 +5343,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -5373,7 +5357,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -5387,7 +5371,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -5401,7 +5385,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -5415,7 +5399,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -5429,7 +5413,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -5443,7 +5427,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -5457,7 +5441,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -5471,7 +5455,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -5485,7 +5469,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -5499,7 +5483,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -5513,7 +5497,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -5527,7 +5511,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -5541,7 +5525,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -5555,7 +5539,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -5569,7 +5553,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -5583,7 +5567,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -5597,7 +5581,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C55" s="3">
         <v>47</v>
       </c>
@@ -5611,12 +5595,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="34" t="s">
         <v>7</v>
       </c>
@@ -5630,7 +5614,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="36">
         <v>1</v>
       </c>
@@ -5644,7 +5628,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="39">
         <v>2</v>
       </c>
@@ -5658,7 +5642,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="36">
         <v>3</v>
       </c>
@@ -5672,7 +5656,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="39">
         <v>4</v>
       </c>
@@ -5686,7 +5670,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="36">
         <v>5</v>
       </c>
@@ -5700,7 +5684,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C64" s="39">
         <v>6</v>
       </c>
@@ -5714,7 +5698,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="65" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C65" s="36">
         <v>7</v>
       </c>
@@ -5728,7 +5712,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="66" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C66" s="39">
         <v>8</v>
       </c>
@@ -5742,7 +5726,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="67" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C67" s="36">
         <v>9</v>
       </c>
@@ -5756,7 +5740,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="68" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C68" s="39">
         <v>10</v>
       </c>
@@ -5770,7 +5754,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="69" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C69" s="36">
         <v>11</v>
       </c>
@@ -5784,7 +5768,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="70" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C70" s="39">
         <v>12</v>
       </c>
@@ -5798,7 +5782,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="71" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C71" s="36">
         <v>13</v>
       </c>
@@ -5812,7 +5796,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="72" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C72" s="39">
         <v>14</v>
       </c>
@@ -5826,7 +5810,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="73" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C73" s="36">
         <v>15</v>
       </c>
@@ -5840,7 +5824,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="74" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C74" s="39">
         <v>16</v>
       </c>
@@ -5854,7 +5838,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="75" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C75" s="36">
         <v>17</v>
       </c>
@@ -5868,7 +5852,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="76" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C76" s="39">
         <v>18</v>
       </c>
@@ -5882,7 +5866,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="77" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C77" s="36">
         <v>19</v>
       </c>
@@ -5896,7 +5880,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="78" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C78" s="39">
         <v>20</v>
       </c>
@@ -5910,7 +5894,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="79" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C79" s="36">
         <v>21</v>
       </c>
@@ -5924,7 +5908,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="80" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C80" s="39">
         <v>22</v>
       </c>
@@ -5938,7 +5922,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="81" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C81" s="36">
         <v>23</v>
       </c>
@@ -5952,7 +5936,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="82" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C82" s="39">
         <v>24</v>
       </c>
@@ -5966,7 +5950,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="83" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C83" s="36">
         <v>25</v>
       </c>
@@ -5980,7 +5964,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="84" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C84" s="39">
         <v>26</v>
       </c>
@@ -5994,7 +5978,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="85" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C85" s="36">
         <v>27</v>
       </c>
@@ -6008,7 +5992,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="86" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C86" s="39">
         <v>28</v>
       </c>
@@ -6022,7 +6006,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="87" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C87" s="36">
         <v>29</v>
       </c>
@@ -6036,7 +6020,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="88" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C88" s="39">
         <v>30</v>
       </c>
@@ -6050,7 +6034,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="89" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C89" s="36">
         <v>31</v>
       </c>
@@ -6064,7 +6048,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="90" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C90" s="39">
         <v>32</v>
       </c>
@@ -6078,7 +6062,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="91" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C91" s="36">
         <v>33</v>
       </c>
@@ -6092,7 +6076,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="92" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C92" s="39">
         <v>34</v>
       </c>
@@ -6106,7 +6090,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="93" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C93" s="36">
         <v>35</v>
       </c>
@@ -6120,7 +6104,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="94" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C94" s="39">
         <v>36</v>
       </c>
@@ -6134,7 +6118,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="95" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C95" s="36">
         <v>37</v>
       </c>
@@ -6148,7 +6132,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="96" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C96" s="39">
         <v>38</v>
       </c>
@@ -6162,7 +6146,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="97" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C97" s="36">
         <v>39</v>
       </c>
@@ -6176,7 +6160,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="98" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C98" s="39">
         <v>40</v>
       </c>
@@ -6190,7 +6174,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="99" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C99" s="36">
         <v>41</v>
       </c>
@@ -6204,7 +6188,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="100" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C100" s="39">
         <v>42</v>
       </c>
@@ -6218,7 +6202,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="101" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C101" s="36">
         <v>43</v>
       </c>
@@ -6232,7 +6216,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="102" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C102" s="39">
         <v>44</v>
       </c>
@@ -6246,7 +6230,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="103" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C103" s="36">
         <v>45</v>
       </c>
@@ -6260,7 +6244,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="104" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C104" s="39">
         <v>46</v>
       </c>
@@ -6274,7 +6258,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="105" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C105" s="36">
         <v>47</v>
       </c>
@@ -6288,7 +6272,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="106" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C106" s="39">
         <v>48</v>
       </c>
@@ -6302,7 +6286,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="107" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C107" s="36">
         <v>49</v>
       </c>
@@ -6316,7 +6300,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="108" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C108" s="39">
         <v>50</v>
       </c>
@@ -6330,7 +6314,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="109" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C109" s="36">
         <v>51</v>
       </c>
@@ -6344,7 +6328,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="110" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C110" s="39">
         <v>52</v>
       </c>
@@ -6358,7 +6342,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="111" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C111" s="36">
         <v>53</v>
       </c>
@@ -6372,7 +6356,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="112" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C112" s="39">
         <v>54</v>
       </c>
@@ -6386,7 +6370,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="113" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C113" s="36">
         <v>55</v>
       </c>
@@ -6400,7 +6384,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="114" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C114" s="39">
         <v>56</v>
       </c>
@@ -6414,7 +6398,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="115" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C115" s="36">
         <v>57</v>
       </c>
@@ -6428,7 +6412,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="116" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C116" s="39">
         <v>58</v>
       </c>
@@ -6442,7 +6426,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="117" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C117" s="36">
         <v>59</v>
       </c>
@@ -6456,7 +6440,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="118" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C118" s="39">
         <v>60</v>
       </c>
@@ -6470,7 +6454,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="119" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C119" s="36">
         <v>61</v>
       </c>
@@ -6484,7 +6468,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="120" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C120" s="39">
         <v>62</v>
       </c>
@@ -6498,7 +6482,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="121" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C121" s="36">
         <v>63</v>
       </c>
@@ -6512,7 +6496,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="122" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C122" s="39">
         <v>64</v>
       </c>
@@ -6526,7 +6510,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="123" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C123" s="36">
         <v>65</v>
       </c>
@@ -6540,7 +6524,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="124" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C124" s="39">
         <v>66</v>
       </c>
@@ -6554,7 +6538,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="125" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C125" s="36">
         <v>67</v>
       </c>
@@ -6568,7 +6552,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="126" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C126" s="39">
         <v>68</v>
       </c>
@@ -6582,7 +6566,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="127" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C127" s="36">
         <v>69</v>
       </c>
@@ -6596,7 +6580,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="128" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C128" s="39">
         <v>70</v>
       </c>
@@ -6610,7 +6594,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="129" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C129" s="36">
         <v>71</v>
       </c>
@@ -6624,7 +6608,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="130" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C130" s="39">
         <v>72</v>
       </c>
@@ -6638,7 +6622,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="131" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C131" s="36">
         <v>73</v>
       </c>
@@ -6652,7 +6636,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="132" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C132" s="39">
         <v>74</v>
       </c>
@@ -6666,7 +6650,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="133" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C133" s="36">
         <v>75</v>
       </c>
@@ -6680,7 +6664,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="134" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C134" s="39">
         <v>76</v>
       </c>
@@ -6694,7 +6678,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="135" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C135" s="36">
         <v>77</v>
       </c>
@@ -6708,7 +6692,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="136" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C136" s="39">
         <v>78</v>
       </c>
@@ -6745,29 +6729,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R137"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>257</v>
       </c>
@@ -6775,7 +6759,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -6783,7 +6767,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -6791,7 +6775,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -6799,13 +6783,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -6813,7 +6797,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -6828,7 +6812,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -6842,7 +6826,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -6856,7 +6840,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -6870,7 +6854,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -6884,7 +6868,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -6898,7 +6882,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -6912,7 +6896,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -6926,7 +6910,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -6940,7 +6924,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -6954,7 +6938,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -6968,7 +6952,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -6982,7 +6966,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -6996,7 +6980,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -7010,7 +6994,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -7024,7 +7008,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -7038,7 +7022,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -7052,7 +7036,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -7066,7 +7050,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -7080,7 +7064,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -7094,7 +7078,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -7108,7 +7092,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -7122,7 +7106,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -7136,7 +7120,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -7150,7 +7134,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -7164,7 +7148,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -7178,7 +7162,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -7192,7 +7176,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -7206,7 +7190,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -7220,7 +7204,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -7234,7 +7218,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -7248,7 +7232,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -7262,7 +7246,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -7276,7 +7260,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -7290,7 +7274,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -7304,7 +7288,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -7318,7 +7302,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -7332,7 +7316,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -7346,7 +7330,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -7360,7 +7344,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -7374,7 +7358,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -7388,7 +7372,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -7402,7 +7386,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -7416,7 +7400,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -7430,7 +7414,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -7444,7 +7428,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -7458,7 +7442,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -7472,12 +7456,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -7491,7 +7475,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -7505,7 +7489,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -7519,7 +7503,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -7533,7 +7517,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -7547,7 +7531,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -7561,7 +7545,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -7575,7 +7559,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -7596,7 +7580,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -7617,7 +7601,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -7638,7 +7622,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -7659,7 +7643,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -7680,7 +7664,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -7701,7 +7685,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -7722,7 +7706,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -7743,7 +7727,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -7764,7 +7748,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -7785,7 +7769,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -7806,7 +7790,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -7827,7 +7811,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -7848,7 +7832,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -7869,7 +7853,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -7890,7 +7874,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -7911,7 +7895,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -7932,7 +7916,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -7953,7 +7937,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -7974,7 +7958,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -7995,7 +7979,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -8016,7 +8000,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -8037,7 +8021,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -8058,7 +8042,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -8079,7 +8063,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -8100,7 +8084,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -8121,7 +8105,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -8142,7 +8126,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -8163,7 +8147,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -8184,7 +8168,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -8205,7 +8189,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -8226,7 +8210,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -8247,7 +8231,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -8268,7 +8252,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -8289,7 +8273,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -8310,7 +8294,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -8331,7 +8315,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -8352,7 +8336,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -8373,7 +8357,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -8394,7 +8378,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -8415,7 +8399,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -8436,7 +8420,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -8457,7 +8441,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -8478,7 +8462,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -8499,7 +8483,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -8520,7 +8504,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -8541,7 +8525,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -8562,7 +8546,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -8583,7 +8567,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -8604,7 +8588,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -8625,7 +8609,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -8646,7 +8630,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -8667,7 +8651,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -8688,7 +8672,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -8709,7 +8693,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -8730,7 +8714,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -8751,7 +8735,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -8772,7 +8756,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -8793,7 +8777,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -8814,7 +8798,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -8835,7 +8819,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -8856,7 +8840,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -8877,7 +8861,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -8898,7 +8882,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -8919,7 +8903,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -8940,7 +8924,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -8961,7 +8945,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -8982,7 +8966,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -9003,7 +8987,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
@@ -9024,7 +9008,7 @@
       <c r="J132" s="30"/>
       <c r="K132" s="30"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C133" s="39">
         <v>76</v>
       </c>
@@ -9038,7 +9022,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C134" s="36">
         <v>77</v>
       </c>
@@ -9052,7 +9036,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C135" s="39">
         <v>78</v>
       </c>
@@ -9066,7 +9050,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C136" s="36">
         <v>79</v>
       </c>
@@ -9080,7 +9064,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C137" s="39">
         <v>80</v>
       </c>
@@ -9117,29 +9101,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R137"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>258</v>
       </c>
@@ -9147,7 +9131,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -9155,7 +9139,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -9163,7 +9147,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -9171,13 +9155,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -9185,7 +9169,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -9200,7 +9184,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -9214,7 +9198,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -9228,7 +9212,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -9242,7 +9226,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -9256,7 +9240,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -9270,7 +9254,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -9284,7 +9268,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -9298,7 +9282,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -9312,7 +9296,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -9326,7 +9310,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -9340,7 +9324,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -9354,7 +9338,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -9368,7 +9352,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -9382,7 +9366,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -9396,7 +9380,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -9410,7 +9394,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -9424,7 +9408,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -9438,7 +9422,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -9452,7 +9436,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -9466,7 +9450,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -9480,7 +9464,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -9494,7 +9478,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -9508,7 +9492,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -9522,7 +9506,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -9536,7 +9520,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -9550,7 +9534,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -9564,7 +9548,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -9578,7 +9562,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -9592,7 +9576,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -9606,7 +9590,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -9620,7 +9604,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -9634,7 +9618,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -9648,7 +9632,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -9662,7 +9646,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -9676,7 +9660,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -9690,7 +9674,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -9704,7 +9688,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -9718,7 +9702,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -9732,7 +9716,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -9746,7 +9730,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -9760,7 +9744,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -9774,7 +9758,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -9788,7 +9772,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -9802,7 +9786,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -9816,7 +9800,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -9830,7 +9814,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -9844,12 +9828,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -9863,7 +9847,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -9877,7 +9861,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -9891,7 +9875,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -9905,7 +9889,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -9919,7 +9903,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -9933,7 +9917,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -9947,7 +9931,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -9968,7 +9952,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -9989,7 +9973,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -10010,7 +9994,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -10031,7 +10015,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -10052,7 +10036,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -10073,7 +10057,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -10094,7 +10078,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -10115,7 +10099,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -10136,7 +10120,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -10157,7 +10141,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -10178,7 +10162,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -10199,7 +10183,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -10220,7 +10204,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -10241,7 +10225,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -10262,7 +10246,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -10283,7 +10267,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -10304,7 +10288,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -10325,7 +10309,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -10346,7 +10330,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -10367,7 +10351,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -10388,7 +10372,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -10409,7 +10393,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -10430,7 +10414,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -10451,7 +10435,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -10472,7 +10456,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -10493,7 +10477,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -10514,7 +10498,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -10535,7 +10519,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -10556,7 +10540,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -10577,7 +10561,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -10598,7 +10582,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -10619,7 +10603,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -10640,7 +10624,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -10661,7 +10645,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -10682,7 +10666,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -10703,7 +10687,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -10724,7 +10708,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -10745,7 +10729,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -10766,7 +10750,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -10787,7 +10771,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -10808,7 +10792,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -10829,7 +10813,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -10850,7 +10834,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -10871,7 +10855,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -10892,7 +10876,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -10913,7 +10897,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -10934,7 +10918,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -10955,7 +10939,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -10976,7 +10960,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -10997,7 +10981,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -11018,7 +11002,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -11039,7 +11023,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -11060,7 +11044,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -11081,7 +11065,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -11102,7 +11086,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -11123,7 +11107,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -11144,7 +11128,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -11165,7 +11149,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -11186,7 +11170,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -11207,7 +11191,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -11228,7 +11212,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -11249,7 +11233,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -11270,7 +11254,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -11291,7 +11275,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -11312,7 +11296,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -11333,7 +11317,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -11354,7 +11338,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -11375,7 +11359,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
@@ -11396,7 +11380,7 @@
       <c r="J132" s="30"/>
       <c r="K132" s="30"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C133" s="39">
         <v>76</v>
       </c>
@@ -11410,7 +11394,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C134" s="36">
         <v>77</v>
       </c>
@@ -11424,7 +11408,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C135" s="39">
         <v>78</v>
       </c>
@@ -11438,7 +11422,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C136" s="36">
         <v>79</v>
       </c>
@@ -11452,7 +11436,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C137" s="39">
         <v>80</v>
       </c>
@@ -11489,29 +11473,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R137"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>259</v>
       </c>
@@ -11519,7 +11503,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -11527,7 +11511,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -11535,7 +11519,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -11543,13 +11527,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -11557,7 +11541,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -11572,7 +11556,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -11586,7 +11570,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -11600,7 +11584,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -11614,7 +11598,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -11628,7 +11612,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -11642,7 +11626,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -11656,7 +11640,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -11670,7 +11654,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -11684,7 +11668,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -11698,7 +11682,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -11712,7 +11696,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -11726,7 +11710,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -11740,7 +11724,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -11754,7 +11738,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -11768,7 +11752,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -11782,7 +11766,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -11796,7 +11780,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -11810,7 +11794,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -11824,7 +11808,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -11838,7 +11822,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -11852,7 +11836,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -11866,7 +11850,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -11880,7 +11864,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -11894,7 +11878,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -11908,7 +11892,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -11922,7 +11906,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -11936,7 +11920,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -11950,7 +11934,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -11964,7 +11948,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -11978,7 +11962,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -11992,7 +11976,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -12006,7 +11990,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -12020,7 +12004,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -12034,7 +12018,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -12048,7 +12032,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -12062,7 +12046,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -12076,7 +12060,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -12090,7 +12074,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -12104,7 +12088,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -12118,7 +12102,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -12132,7 +12116,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -12146,7 +12130,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -12160,7 +12144,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -12174,7 +12158,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -12188,7 +12172,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -12202,7 +12186,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -12216,12 +12200,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -12235,7 +12219,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -12249,7 +12233,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -12263,7 +12247,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -12277,7 +12261,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -12291,7 +12275,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -12305,7 +12289,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -12319,7 +12303,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -12340,7 +12324,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -12361,7 +12345,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -12382,7 +12366,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -12403,7 +12387,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -12424,7 +12408,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -12445,7 +12429,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -12466,7 +12450,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -12487,7 +12471,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -12508,7 +12492,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -12529,7 +12513,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -12550,7 +12534,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -12571,7 +12555,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -12592,7 +12576,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -12613,7 +12597,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -12634,7 +12618,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -12655,7 +12639,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -12676,7 +12660,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -12697,7 +12681,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -12718,7 +12702,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -12739,7 +12723,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -12760,7 +12744,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -12781,7 +12765,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -12802,7 +12786,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -12823,7 +12807,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -12844,7 +12828,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -12865,7 +12849,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -12886,7 +12870,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -12907,7 +12891,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -12928,7 +12912,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -12949,7 +12933,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -12970,7 +12954,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -12991,7 +12975,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -13012,7 +12996,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -13033,7 +13017,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -13054,7 +13038,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -13075,7 +13059,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -13096,7 +13080,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -13117,7 +13101,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -13138,7 +13122,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -13159,7 +13143,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -13180,7 +13164,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -13201,7 +13185,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -13222,7 +13206,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -13243,7 +13227,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -13264,7 +13248,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -13285,7 +13269,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -13306,7 +13290,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -13327,7 +13311,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -13348,7 +13332,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -13369,7 +13353,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -13390,7 +13374,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -13411,7 +13395,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -13432,7 +13416,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -13453,7 +13437,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -13474,7 +13458,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -13495,7 +13479,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -13516,7 +13500,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -13537,7 +13521,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -13558,7 +13542,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -13579,7 +13563,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -13600,7 +13584,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -13621,7 +13605,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -13642,7 +13626,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -13663,7 +13647,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -13684,7 +13668,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -13705,7 +13689,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -13726,7 +13710,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -13747,7 +13731,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
@@ -13768,7 +13752,7 @@
       <c r="J132" s="30"/>
       <c r="K132" s="30"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C133" s="39">
         <v>76</v>
       </c>
@@ -13782,7 +13766,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C134" s="36">
         <v>77</v>
       </c>
@@ -13796,7 +13780,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C135" s="3">
         <v>78</v>
       </c>
@@ -13810,7 +13794,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C136" s="36">
         <v>79</v>
       </c>
@@ -13824,7 +13808,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C137" s="3">
         <v>80</v>
       </c>
@@ -13861,29 +13845,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R137"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>260</v>
       </c>
@@ -13891,7 +13875,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -13899,7 +13883,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -13907,7 +13891,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -13915,13 +13899,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -13929,7 +13913,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -13944,7 +13928,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -13958,7 +13942,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -13972,7 +13956,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -13986,7 +13970,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -14000,7 +13984,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -14014,7 +13998,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -14028,7 +14012,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -14042,7 +14026,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -14056,7 +14040,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -14070,7 +14054,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -14084,7 +14068,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -14098,7 +14082,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -14112,7 +14096,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -14126,7 +14110,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -14140,7 +14124,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -14154,7 +14138,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -14168,7 +14152,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -14182,7 +14166,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -14196,7 +14180,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -14210,7 +14194,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -14224,7 +14208,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -14238,7 +14222,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -14252,7 +14236,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -14266,7 +14250,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -14280,7 +14264,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -14294,7 +14278,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -14308,7 +14292,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -14322,7 +14306,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -14336,7 +14320,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -14350,7 +14334,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -14364,7 +14348,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -14378,7 +14362,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -14392,7 +14376,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -14406,7 +14390,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -14420,7 +14404,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -14434,7 +14418,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -14448,7 +14432,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -14462,7 +14446,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -14476,7 +14460,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -14490,7 +14474,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -14504,7 +14488,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -14518,7 +14502,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -14532,7 +14516,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -14546,7 +14530,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -14560,7 +14544,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -14574,7 +14558,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -14588,12 +14572,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -14607,7 +14591,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -14621,7 +14605,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -14635,7 +14619,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -14649,7 +14633,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -14663,7 +14647,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -14677,7 +14661,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -14691,7 +14675,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -14712,7 +14696,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -14733,7 +14717,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -14754,7 +14738,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -14775,7 +14759,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -14796,7 +14780,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -14817,7 +14801,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -14838,7 +14822,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -14859,7 +14843,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -14880,7 +14864,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -14901,7 +14885,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -14922,7 +14906,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -14943,7 +14927,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -14964,7 +14948,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -14985,7 +14969,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -15006,7 +14990,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -15027,7 +15011,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -15048,7 +15032,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -15069,7 +15053,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -15090,7 +15074,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -15111,7 +15095,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -15132,7 +15116,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -15153,7 +15137,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -15174,7 +15158,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -15195,7 +15179,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -15216,7 +15200,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -15237,7 +15221,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -15258,7 +15242,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -15279,7 +15263,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -15300,7 +15284,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -15321,7 +15305,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -15342,7 +15326,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -15363,7 +15347,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -15384,7 +15368,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -15405,7 +15389,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -15426,7 +15410,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -15447,7 +15431,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -15468,7 +15452,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -15489,7 +15473,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -15510,7 +15494,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -15531,7 +15515,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -15552,7 +15536,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -15573,7 +15557,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -15594,7 +15578,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -15615,7 +15599,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -15636,7 +15620,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -15657,7 +15641,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -15678,7 +15662,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -15699,7 +15683,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -15720,7 +15704,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -15741,7 +15725,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -15762,7 +15746,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -15783,7 +15767,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -15804,7 +15788,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -15825,7 +15809,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -15846,7 +15830,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -15867,7 +15851,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -15888,7 +15872,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -15909,7 +15893,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -15930,7 +15914,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -15951,7 +15935,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -15972,7 +15956,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -15993,7 +15977,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -16014,7 +15998,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -16035,7 +16019,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -16056,7 +16040,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -16077,7 +16061,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -16098,7 +16082,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -16119,7 +16103,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
@@ -16140,7 +16124,7 @@
       <c r="J132" s="30"/>
       <c r="K132" s="30"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C133" s="39">
         <v>76</v>
       </c>
@@ -16154,7 +16138,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C134" s="36">
         <v>77</v>
       </c>
@@ -16168,7 +16152,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C135" s="3">
         <v>78</v>
       </c>
@@ -16182,7 +16166,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C136" s="36">
         <v>79</v>
       </c>
@@ -16196,7 +16180,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C137" s="3">
         <v>80</v>
       </c>
@@ -16233,29 +16217,29 @@
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R137"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="30" customWidth="1"/>
-    <col min="2" max="2" width="0.86328125" style="28" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="130.6640625" style="33" customWidth="1"/>
-    <col min="5" max="5" width="50.6640625" style="33" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="30" customWidth="1"/>
-    <col min="8" max="9" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="2.69140625" style="30" customWidth="1"/>
+    <col min="2" max="2" width="0.84375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="130.69140625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="50.69140625" style="33" customWidth="1"/>
+    <col min="6" max="6" width="30.69140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="2.69140625" style="30" customWidth="1"/>
+    <col min="8" max="9" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="15" max="16" width="9.1328125" style="30" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="9.15234375" style="30" hidden="1" customWidth="1"/>
     <col min="17" max="18" width="0" style="30" hidden="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.1328125" style="30" hidden="1"/>
+    <col min="19" max="16384" width="9.15234375" style="30" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" s="1" customFormat="1" ht="80.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C2" s="4" t="s">
         <v>261</v>
       </c>
@@ -16263,7 +16247,7 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
     </row>
-    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C3" s="25" t="s">
         <v>226</v>
       </c>
@@ -16271,7 +16255,7 @@
       <c r="E3" s="26"/>
       <c r="F3" s="26"/>
     </row>
-    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C4" s="27"/>
       <c r="D4" s="27" t="s">
         <v>227</v>
@@ -16279,7 +16263,7 @@
       <c r="E4" s="26"/>
       <c r="F4" s="26"/>
     </row>
-    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C5" s="27"/>
       <c r="D5" s="27" t="s">
         <v>16</v>
@@ -16287,13 +16271,13 @@
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
     </row>
-    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C6" s="27"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
     </row>
-    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" s="24" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C7" s="27" t="s">
         <v>227</v>
       </c>
@@ -16301,7 +16285,7 @@
       <c r="E7" s="26"/>
       <c r="F7" s="26"/>
     </row>
-    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="8"/>
       <c r="C8" s="12" t="s">
         <v>7</v>
@@ -16316,7 +16300,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" s="3">
         <v>1</v>
       </c>
@@ -16330,7 +16314,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C10" s="3">
         <v>2</v>
       </c>
@@ -16344,7 +16328,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C11" s="3">
         <v>3</v>
       </c>
@@ -16358,7 +16342,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C12" s="3">
         <v>4</v>
       </c>
@@ -16372,7 +16356,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C13" s="3">
         <v>5</v>
       </c>
@@ -16386,7 +16370,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <v>6</v>
       </c>
@@ -16400,7 +16384,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C15" s="3">
         <v>7</v>
       </c>
@@ -16414,7 +16398,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C16" s="3">
         <v>8</v>
       </c>
@@ -16428,7 +16412,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C17" s="3">
         <v>9</v>
       </c>
@@ -16442,7 +16426,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C18" s="3">
         <v>10</v>
       </c>
@@ -16456,7 +16440,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C19" s="3">
         <v>11</v>
       </c>
@@ -16470,7 +16454,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C20" s="3">
         <v>12</v>
       </c>
@@ -16484,7 +16468,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C21" s="3">
         <v>13</v>
       </c>
@@ -16498,7 +16482,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C22" s="3">
         <v>14</v>
       </c>
@@ -16512,7 +16496,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C23" s="3">
         <v>15</v>
       </c>
@@ -16526,7 +16510,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C24" s="3">
         <v>16</v>
       </c>
@@ -16540,7 +16524,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C25" s="3">
         <v>17</v>
       </c>
@@ -16554,7 +16538,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C26" s="3">
         <v>18</v>
       </c>
@@ -16568,7 +16552,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C27" s="3">
         <v>19</v>
       </c>
@@ -16582,7 +16566,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C28" s="3">
         <v>20</v>
       </c>
@@ -16596,7 +16580,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C29" s="3">
         <v>21</v>
       </c>
@@ -16610,7 +16594,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C30" s="3">
         <v>22</v>
       </c>
@@ -16624,7 +16608,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C31" s="3">
         <v>23</v>
       </c>
@@ -16638,7 +16622,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="3:6" s="28" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C32" s="3">
         <v>24</v>
       </c>
@@ -16652,7 +16636,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C33" s="3">
         <v>25</v>
       </c>
@@ -16666,7 +16650,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C34" s="3">
         <v>26</v>
       </c>
@@ -16680,7 +16664,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C35" s="3">
         <v>27</v>
       </c>
@@ -16694,7 +16678,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C36" s="3">
         <v>28</v>
       </c>
@@ -16708,7 +16692,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C37" s="3">
         <v>29</v>
       </c>
@@ -16722,7 +16706,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C38" s="3">
         <v>30</v>
       </c>
@@ -16736,7 +16720,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C39" s="3">
         <v>31</v>
       </c>
@@ -16750,7 +16734,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C40" s="3">
         <v>32</v>
       </c>
@@ -16764,7 +16748,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C41" s="3">
         <v>33</v>
       </c>
@@ -16778,7 +16762,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C42" s="3">
         <v>34</v>
       </c>
@@ -16792,7 +16776,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C43" s="3">
         <v>35</v>
       </c>
@@ -16806,7 +16790,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C44" s="3">
         <v>36</v>
       </c>
@@ -16820,7 +16804,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C45" s="3">
         <v>37</v>
       </c>
@@ -16834,7 +16818,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C46" s="3">
         <v>38</v>
       </c>
@@ -16848,7 +16832,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C47" s="3">
         <v>39</v>
       </c>
@@ -16862,7 +16846,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="3:6" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C48" s="3">
         <v>40</v>
       </c>
@@ -16876,7 +16860,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C49" s="3">
         <v>41</v>
       </c>
@@ -16890,7 +16874,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C50" s="3">
         <v>42</v>
       </c>
@@ -16904,7 +16888,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C51" s="3">
         <v>43</v>
       </c>
@@ -16918,7 +16902,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C52" s="3">
         <v>44</v>
       </c>
@@ -16932,7 +16916,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C53" s="3">
         <v>45</v>
       </c>
@@ -16946,7 +16930,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C54" s="3">
         <v>46</v>
       </c>
@@ -16960,12 +16944,12 @@
         <v>158</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C57" s="34" t="s">
         <v>7</v>
       </c>
@@ -16979,7 +16963,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C58" s="36">
         <v>1</v>
       </c>
@@ -16993,7 +16977,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C59" s="39">
         <v>2</v>
       </c>
@@ -17007,7 +16991,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C60" s="36">
         <v>3</v>
       </c>
@@ -17021,7 +17005,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C61" s="39">
         <v>4</v>
       </c>
@@ -17035,7 +17019,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C62" s="36">
         <v>5</v>
       </c>
@@ -17049,7 +17033,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C63" s="39">
         <v>6</v>
       </c>
@@ -17063,7 +17047,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="30"/>
       <c r="B64" s="28"/>
       <c r="C64" s="36">
@@ -17084,7 +17068,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="30"/>
       <c r="B65" s="28"/>
       <c r="C65" s="39">
@@ -17105,7 +17089,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="30"/>
       <c r="B66" s="28"/>
       <c r="C66" s="36">
@@ -17126,7 +17110,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="30"/>
       <c r="B67" s="28"/>
       <c r="C67" s="39">
@@ -17147,7 +17131,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="30"/>
       <c r="B68" s="28"/>
       <c r="C68" s="36">
@@ -17168,7 +17152,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="30"/>
       <c r="B69" s="28"/>
       <c r="C69" s="39">
@@ -17189,7 +17173,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="30"/>
       <c r="B70" s="28"/>
       <c r="C70" s="36">
@@ -17210,7 +17194,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="30"/>
       <c r="B71" s="28"/>
       <c r="C71" s="39">
@@ -17231,7 +17215,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="30"/>
       <c r="B72" s="28"/>
       <c r="C72" s="36">
@@ -17252,7 +17236,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="30"/>
       <c r="B73" s="28"/>
       <c r="C73" s="39">
@@ -17273,7 +17257,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="30"/>
       <c r="B74" s="28"/>
       <c r="C74" s="36">
@@ -17294,7 +17278,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="30"/>
       <c r="B75" s="28"/>
       <c r="C75" s="39">
@@ -17315,7 +17299,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="30"/>
       <c r="B76" s="28"/>
       <c r="C76" s="36">
@@ -17336,7 +17320,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="30"/>
       <c r="B77" s="28"/>
       <c r="C77" s="39">
@@ -17357,7 +17341,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="30"/>
       <c r="B78" s="28"/>
       <c r="C78" s="36">
@@ -17378,7 +17362,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="30"/>
       <c r="B79" s="28"/>
       <c r="C79" s="39">
@@ -17399,7 +17383,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="30"/>
       <c r="B80" s="28"/>
       <c r="C80" s="36">
@@ -17420,7 +17404,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="30"/>
       <c r="B81" s="28"/>
       <c r="C81" s="39">
@@ -17441,7 +17425,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="30"/>
       <c r="B82" s="28"/>
       <c r="C82" s="36">
@@ -17462,7 +17446,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="30"/>
       <c r="B83" s="28"/>
       <c r="C83" s="39">
@@ -17483,7 +17467,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="30"/>
       <c r="B84" s="28"/>
       <c r="C84" s="36">
@@ -17504,7 +17488,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="30"/>
       <c r="B85" s="28"/>
       <c r="C85" s="39">
@@ -17525,7 +17509,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="30"/>
       <c r="B86" s="28"/>
       <c r="C86" s="36">
@@ -17546,7 +17530,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="30"/>
       <c r="B87" s="28"/>
       <c r="C87" s="39">
@@ -17567,7 +17551,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="30"/>
       <c r="B88" s="28"/>
       <c r="C88" s="36">
@@ -17588,7 +17572,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="30"/>
       <c r="B89" s="28"/>
       <c r="C89" s="39">
@@ -17609,7 +17593,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A90" s="30"/>
       <c r="B90" s="28"/>
       <c r="C90" s="36">
@@ -17630,7 +17614,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A91" s="30"/>
       <c r="B91" s="28"/>
       <c r="C91" s="39">
@@ -17651,7 +17635,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A92" s="30"/>
       <c r="B92" s="28"/>
       <c r="C92" s="36">
@@ -17672,7 +17656,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A93" s="30"/>
       <c r="B93" s="28"/>
       <c r="C93" s="39">
@@ -17693,7 +17677,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A94" s="30"/>
       <c r="B94" s="28"/>
       <c r="C94" s="36">
@@ -17714,7 +17698,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A95" s="30"/>
       <c r="B95" s="28"/>
       <c r="C95" s="39">
@@ -17735,7 +17719,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A96" s="30"/>
       <c r="B96" s="28"/>
       <c r="C96" s="36">
@@ -17756,7 +17740,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A97" s="30"/>
       <c r="B97" s="28"/>
       <c r="C97" s="39">
@@ -17777,7 +17761,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A98" s="30"/>
       <c r="B98" s="28"/>
       <c r="C98" s="36">
@@ -17798,7 +17782,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A99" s="30"/>
       <c r="B99" s="28"/>
       <c r="C99" s="39">
@@ -17819,7 +17803,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A100" s="30"/>
       <c r="B100" s="28"/>
       <c r="C100" s="36">
@@ -17840,7 +17824,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A101" s="30"/>
       <c r="B101" s="28"/>
       <c r="C101" s="39">
@@ -17861,7 +17845,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A102" s="30"/>
       <c r="B102" s="28"/>
       <c r="C102" s="36">
@@ -17882,7 +17866,7 @@
       <c r="J102" s="30"/>
       <c r="K102" s="30"/>
     </row>
-    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A103" s="30"/>
       <c r="B103" s="28"/>
       <c r="C103" s="39">
@@ -17903,7 +17887,7 @@
       <c r="J103" s="30"/>
       <c r="K103" s="30"/>
     </row>
-    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A104" s="30"/>
       <c r="B104" s="28"/>
       <c r="C104" s="36">
@@ -17924,7 +17908,7 @@
       <c r="J104" s="30"/>
       <c r="K104" s="30"/>
     </row>
-    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A105" s="30"/>
       <c r="B105" s="28"/>
       <c r="C105" s="39">
@@ -17945,7 +17929,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A106" s="30"/>
       <c r="B106" s="28"/>
       <c r="C106" s="36">
@@ -17966,7 +17950,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A107" s="30"/>
       <c r="B107" s="28"/>
       <c r="C107" s="39">
@@ -17987,7 +17971,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A108" s="30"/>
       <c r="B108" s="28"/>
       <c r="C108" s="36">
@@ -18008,7 +17992,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A109" s="30"/>
       <c r="B109" s="28"/>
       <c r="C109" s="39">
@@ -18029,7 +18013,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A110" s="30"/>
       <c r="B110" s="28"/>
       <c r="C110" s="36">
@@ -18050,7 +18034,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A111" s="30"/>
       <c r="B111" s="28"/>
       <c r="C111" s="39">
@@ -18071,7 +18055,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A112" s="30"/>
       <c r="B112" s="28"/>
       <c r="C112" s="36">
@@ -18092,7 +18076,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A113" s="30"/>
       <c r="B113" s="28"/>
       <c r="C113" s="39">
@@ -18113,7 +18097,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A114" s="30"/>
       <c r="B114" s="28"/>
       <c r="C114" s="36">
@@ -18134,7 +18118,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A115" s="30"/>
       <c r="B115" s="28"/>
       <c r="C115" s="39">
@@ -18155,7 +18139,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A116" s="30"/>
       <c r="B116" s="28"/>
       <c r="C116" s="36">
@@ -18176,7 +18160,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A117" s="30"/>
       <c r="B117" s="28"/>
       <c r="C117" s="39">
@@ -18197,7 +18181,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A118" s="30"/>
       <c r="B118" s="28"/>
       <c r="C118" s="36">
@@ -18218,7 +18202,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A119" s="30"/>
       <c r="B119" s="28"/>
       <c r="C119" s="39">
@@ -18239,7 +18223,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A120" s="30"/>
       <c r="B120" s="28"/>
       <c r="C120" s="36">
@@ -18260,7 +18244,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A121" s="30"/>
       <c r="B121" s="28"/>
       <c r="C121" s="39">
@@ -18281,7 +18265,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A122" s="30"/>
       <c r="B122" s="28"/>
       <c r="C122" s="36">
@@ -18302,7 +18286,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A123" s="30"/>
       <c r="B123" s="28"/>
       <c r="C123" s="39">
@@ -18323,7 +18307,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A124" s="30"/>
       <c r="B124" s="28"/>
       <c r="C124" s="36">
@@ -18344,7 +18328,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A125" s="30"/>
       <c r="B125" s="28"/>
       <c r="C125" s="39">
@@ -18365,7 +18349,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A126" s="30"/>
       <c r="B126" s="28"/>
       <c r="C126" s="36">
@@ -18386,7 +18370,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A127" s="30"/>
       <c r="B127" s="28"/>
       <c r="C127" s="39">
@@ -18407,7 +18391,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A128" s="30"/>
       <c r="B128" s="28"/>
       <c r="C128" s="36">
@@ -18428,7 +18412,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A129" s="30"/>
       <c r="B129" s="28"/>
       <c r="C129" s="39">
@@ -18449,7 +18433,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A130" s="30"/>
       <c r="B130" s="28"/>
       <c r="C130" s="36">
@@ -18470,7 +18454,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A131" s="30"/>
       <c r="B131" s="28"/>
       <c r="C131" s="39">
@@ -18491,7 +18475,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:11" s="8" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A132" s="30"/>
       <c r="B132" s="28"/>
       <c r="C132" s="36">
@@ -18512,7 +18496,7 @@
       <c r="J132" s="30"/>
       <c r="K132" s="30"/>
     </row>
-    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C133" s="39">
         <v>76</v>
       </c>
@@ -18526,7 +18510,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C134" s="36">
         <v>77</v>
       </c>
@@ -18540,7 +18524,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C135" s="3">
         <v>78</v>
       </c>
@@ -18554,7 +18538,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C136" s="36">
         <v>79</v>
       </c>
@@ -18568,7 +18552,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:11" ht="42" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C137" s="3">
         <v>80</v>
       </c>
